--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="24030" windowHeight="9210"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -166,10 +166,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -181,24 +181,84 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -211,12 +271,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -224,6 +285,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -231,47 +307,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,52 +330,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -340,197 +340,212 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -545,54 +560,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,6 +590,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -631,156 +622,183 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1137,78 +1155,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60">
   <si>
     <t>##var</t>
   </si>
@@ -35,6 +35,15 @@
     <t>CleanStrategy</t>
   </si>
   <si>
+    <t>LogicType</t>
+  </si>
+  <si>
+    <t>IfActive</t>
+  </si>
+  <si>
+    <t>ShowOrder</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -53,9 +62,21 @@
     <t>ERedDotCleanStrategy</t>
   </si>
   <si>
+    <t>ERedDotLogicType</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -74,12 +95,24 @@
     <t>清理策略</t>
   </si>
   <si>
+    <t>计算逻辑类型</t>
+  </si>
+  <si>
+    <t>是否激活</t>
+  </si>
+  <si>
+    <t>显示优先级</t>
+  </si>
+  <si>
     <t>DotOnly=0 DotNumber=1 Auto=2</t>
   </si>
   <si>
     <t>Manual=0 ViewAutoClean=1</t>
   </si>
   <si>
+    <t>Sum=0, Any=1</t>
+  </si>
+  <si>
     <t>Bag</t>
   </si>
   <si>
@@ -90,6 +123,9 @@
   </si>
   <si>
     <t>Manual</t>
+  </si>
+  <si>
+    <t>Sum</t>
   </si>
   <si>
     <t>Bag_Item</t>
@@ -166,8 +202,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -188,59 +224,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,11 +238,85 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -270,56 +328,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,6 +343,29 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -346,175 +382,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,54 +581,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -632,6 +620,54 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -652,10 +688,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,140 +700,146 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1145,16 +1187,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="4" width="21.75" customWidth="1"/>
     <col min="5" max="5" width="30.25" customWidth="1"/>
     <col min="6" max="6" width="25.25" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,261 +1218,420 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:9">
       <c r="B6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:9">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:9">
       <c r="B8" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>3</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:9">
       <c r="B10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4</v>
       </c>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:9">
       <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
         <v>34</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" t="s">
-        <v>24</v>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:9">
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>6</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:9">
       <c r="B13" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" t="s">
         <v>36</v>
       </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>24</v>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:9">
       <c r="B14" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" t="s">
         <v>36</v>
       </c>
-      <c r="E14" t="s">
-        <v>23</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:9">
       <c r="B15" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" t="s">
         <v>36</v>
       </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
-        <v>24</v>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>9</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:9">
       <c r="B16" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:9">
       <c r="B17" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowHeight="18450"/>
+    <workbookView windowWidth="24750" windowHeight="10965"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>LogicType</t>
   </si>
   <si>
-    <t>IfActive</t>
+    <t>IsActive</t>
   </si>
   <si>
     <t>ShowOrder</t>
@@ -202,10 +202,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -223,8 +223,129 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,130 +359,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -382,181 +382,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,6 +581,54 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,39 +662,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -667,31 +682,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,143 +700,140 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1195,7 +1192,7 @@
     <col min="5" max="5" width="30.25" customWidth="1"/>
     <col min="6" max="6" width="25.25" customWidth="1"/>
     <col min="7" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="10.625" customWidth="1"/>
+    <col min="8" max="8" width="11.25" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1353,7 +1350,7 @@
       <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1379,7 +1376,7 @@
       <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1405,7 +1402,7 @@
       <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1428,7 +1425,7 @@
       <c r="H9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>3</v>
       </c>
     </row>
@@ -1454,7 +1451,7 @@
       <c r="H10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>4</v>
       </c>
     </row>
@@ -1480,7 +1477,7 @@
       <c r="H11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>5</v>
       </c>
     </row>
@@ -1503,7 +1500,7 @@
       <c r="H12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <v>6</v>
       </c>
     </row>
@@ -1529,7 +1526,7 @@
       <c r="H13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>7</v>
       </c>
     </row>
@@ -1555,7 +1552,7 @@
       <c r="H14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>8</v>
       </c>
     </row>
@@ -1581,7 +1578,7 @@
       <c r="H15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="2">
         <v>9</v>
       </c>
     </row>
@@ -1604,7 +1601,7 @@
       <c r="H16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="2">
         <v>10</v>
       </c>
     </row>
@@ -1630,7 +1627,7 @@
       <c r="H17" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="2">
         <v>11</v>
       </c>
     </row>

--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10965"/>
+    <workbookView windowHeight="18450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57">
   <si>
     <t>##var</t>
   </si>
@@ -41,9 +41,6 @@
     <t>IsActive</t>
   </si>
   <si>
-    <t>ShowOrder</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -68,9 +65,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -89,19 +83,16 @@
     <t>父节点ID(空=根节点)</t>
   </si>
   <si>
-    <t>显示模式</t>
-  </si>
-  <si>
-    <t>清理策略</t>
-  </si>
-  <si>
-    <t>计算逻辑类型</t>
-  </si>
-  <si>
-    <t>是否激活</t>
-  </si>
-  <si>
-    <t>显示优先级</t>
+    <t>显示模式(仅显示红点/红点数目/自动)</t>
+  </si>
+  <si>
+    <t>清理策略(手动/看过即清理)</t>
+  </si>
+  <si>
+    <t>计算逻辑类型(求和/任意一个即可)</t>
+  </si>
+  <si>
+    <t>是否激活(总开关)</t>
   </si>
   <si>
     <t>DotOnly=0 DotNumber=1 Auto=2</t>
@@ -202,8 +193,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
@@ -223,23 +214,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,6 +250,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -267,6 +265,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -276,22 +275,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -305,6 +305,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -313,55 +321,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -382,25 +373,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,25 +523,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,121 +547,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -581,30 +572,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,6 +600,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -650,20 +652,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -688,10 +679,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,133 +691,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1189,14 +1180,14 @@
   <cols>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="4" width="21.75" customWidth="1"/>
-    <col min="5" max="5" width="30.25" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="25.25" customWidth="1"/>
-    <col min="7" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="31.375" customWidth="1"/>
+    <col min="8" max="8" width="18.125" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1221,415 +1212,378 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" ht="23" customHeight="1" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
         <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
       </c>
       <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" t="s">
-        <v>35</v>
-      </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="2">
-        <v>1</v>
-      </c>
+      <c r="I7" s="2"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>35</v>
-      </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="2">
-        <v>2</v>
-      </c>
+      <c r="I8" s="2"/>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="2">
-        <v>3</v>
-      </c>
+      <c r="I9" s="2"/>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="2">
-        <v>4</v>
-      </c>
+      <c r="I10" s="2"/>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="2">
-        <v>5</v>
-      </c>
+      <c r="I11" s="2"/>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="2">
-        <v>6</v>
-      </c>
+      <c r="I12" s="2"/>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="2">
-        <v>7</v>
-      </c>
+      <c r="I13" s="2"/>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="2">
-        <v>8</v>
-      </c>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="2:9">
       <c r="B15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="2">
-        <v>9</v>
-      </c>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:9">
       <c r="B16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H16" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="2">
-        <v>10</v>
-      </c>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="I17" s="2">
-        <v>11</v>
-      </c>
+      <c r="I17" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -83,25 +83,29 @@
     <t>父节点ID(空=根节点)</t>
   </si>
   <si>
-    <t>显示模式(仅显示红点/红点数目/自动)</t>
-  </si>
-  <si>
-    <t>清理策略(手动/看过即清理)</t>
-  </si>
-  <si>
-    <t>计算逻辑类型(求和/任意一个即可)</t>
+    <t>显示模式</t>
+  </si>
+  <si>
+    <t>清除策略</t>
+  </si>
+  <si>
+    <t>计算逻辑类型</t>
   </si>
   <si>
     <t>是否激活(总开关)</t>
   </si>
   <si>
-    <t>DotOnly=0 DotNumber=1 Auto=2</t>
-  </si>
-  <si>
-    <t>Manual=0 ViewAutoClean=1</t>
-  </si>
-  <si>
-    <t>Sum=0, Any=1</t>
+    <t>DotOnly:仅显示红点 
+DotNumber:红点+数字 
+Auto：红点数&gt;1时才显示数字，否则只显示红点</t>
+  </si>
+  <si>
+    <t>Manual:手动清除(业务逻辑代码判断) 
+ViewAutoClean=1:看过自动清除</t>
+  </si>
+  <si>
+    <t>Sum:所有节点求和
+ Any:任意一个节点有</t>
   </si>
   <si>
     <t>Bag</t>
@@ -193,10 +197,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -215,12 +219,110 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -228,10 +330,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -243,116 +354,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -373,78 +377,168 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -458,96 +552,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,9 +582,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,26 +615,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -631,21 +626,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -673,158 +653,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="31" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1180,8 +1187,8 @@
   <cols>
     <col min="2" max="2" width="15.375" customWidth="1"/>
     <col min="3" max="4" width="21.75" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="25.25" customWidth="1"/>
+    <col min="5" max="5" width="41.25" customWidth="1"/>
+    <col min="6" max="6" width="32.75" customWidth="1"/>
     <col min="7" max="7" width="31.375" customWidth="1"/>
     <col min="8" max="8" width="18.125" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
@@ -1291,17 +1298,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="23" customHeight="1" spans="1:8">
+    <row r="5" ht="53" customHeight="1" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1325,10 +1332,10 @@
       <c r="G6" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="2" t="b">
+      <c r="H6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" t="s">
@@ -1349,10 +1356,10 @@
       <c r="G7" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I7" s="2"/>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
@@ -1373,10 +1380,10 @@
       <c r="G8" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="2" t="b">
+      <c r="H8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
@@ -1394,10 +1401,10 @@
       <c r="G9" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
@@ -1418,10 +1425,10 @@
       <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="2" t="b">
+      <c r="H10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="3"/>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
@@ -1442,10 +1449,10 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="2" t="b">
+      <c r="H11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="3"/>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
@@ -1463,10 +1470,10 @@
       <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="2" t="b">
+      <c r="H12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="3"/>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" t="s">
@@ -1487,10 +1494,10 @@
       <c r="G13" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="2" t="b">
+      <c r="H13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="3"/>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" t="s">
@@ -1511,10 +1518,10 @@
       <c r="G14" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="2" t="b">
+      <c r="H14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="2:9">
       <c r="B15" t="s">
@@ -1535,10 +1542,10 @@
       <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="2" t="b">
+      <c r="H15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="3"/>
     </row>
     <row r="16" spans="2:9">
       <c r="B16" t="s">
@@ -1556,10 +1563,10 @@
       <c r="G16" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="2" t="b">
+      <c r="H16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17" spans="2:9">
       <c r="B17" t="s">
@@ -1580,10 +1587,10 @@
       <c r="G17" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="2" t="b">
+      <c r="H17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Config/Excels/Tables/R-RedDot-红点表.xlsx
+++ b/Config/Excels/Tables/R-RedDot-红点表.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64">
   <si>
     <t>##var</t>
   </si>
@@ -136,6 +136,27 @@
   </si>
   <si>
     <t>背包.技能</t>
+  </si>
+  <si>
+    <t>Bag_Skill_Active</t>
+  </si>
+  <si>
+    <t>背包.技能.主动</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Bag_Skill_BeActive</t>
+  </si>
+  <si>
+    <t>背包.技能.被动</t>
+  </si>
+  <si>
+    <t>Bag_Skill_Active_Play</t>
+  </si>
+  <si>
+    <t>背包.技能.主动.释放</t>
   </si>
   <si>
     <t>Shop</t>
@@ -197,10 +218,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -234,20 +255,35 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -255,46 +291,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,33 +306,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -346,17 +337,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -377,12 +398,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -390,168 +573,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +601,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -591,11 +636,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,17 +666,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,175 +698,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1182,15 +1203,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="24.875" customWidth="1"/>
     <col min="3" max="4" width="21.75" customWidth="1"/>
     <col min="5" max="5" width="41.25" customWidth="1"/>
     <col min="6" max="6" width="32.75" customWidth="1"/>
-    <col min="7" max="7" width="31.375" customWidth="1"/>
-    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
     <col min="9" max="9" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1392,8 +1413,11 @@
       <c r="C9" t="s">
         <v>40</v>
       </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
         <v>32</v>
@@ -1408,16 +1432,16 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
       </c>
       <c r="F10" t="s">
         <v>32</v>
@@ -1432,16 +1456,16 @@
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
@@ -1456,13 +1480,13 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>32</v>
@@ -1477,13 +1501,13 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
         <v>31</v>
@@ -1501,13 +1525,13 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
         <v>31</v>
@@ -1525,13 +1549,10 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
         <v>31</v>
@@ -1549,10 +1570,13 @@
     </row>
     <row r="16" spans="2:9">
       <c r="B16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
       </c>
       <c r="E16" t="s">
         <v>31</v>
@@ -1570,13 +1594,13 @@
     </row>
     <row r="17" spans="2:9">
       <c r="B17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="s">
         <v>31</v>
@@ -1591,6 +1615,75 @@
         <v>1</v>
       </c>
       <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
